--- a/Track_Information.xlsx
+++ b/Track_Information.xlsx
@@ -1,149 +1,55 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\darin\Desktop\Racing\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19D8B1E3-4B18-49DA-A658-0B58D27E0A03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="23880" yWindow="-3270" windowWidth="29040" windowHeight="18240" xr2:uid="{4B673ACD-6BA4-41B9-AA5D-B57F4ACFA004}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="23880" yWindow="-3270" windowWidth="29040" windowHeight="18240" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="181029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
-  <si>
-    <t>Track Name</t>
-  </si>
-  <si>
-    <t>Track ID</t>
-  </si>
-  <si>
-    <t>Length (ft)</t>
-  </si>
-  <si>
-    <t>Indianapolis</t>
-  </si>
-  <si>
-    <t>indianapolis 2022 road</t>
-  </si>
-  <si>
-    <t>Mobility Resort</t>
-  </si>
-  <si>
-    <t>twinring fullrc</t>
-  </si>
-  <si>
-    <t>Monza</t>
-  </si>
-  <si>
-    <t>monza full</t>
-  </si>
-  <si>
-    <t>Road Atlanta</t>
-  </si>
-  <si>
-    <t>roadatlanta full</t>
-  </si>
-  <si>
-    <t>Sachsenring</t>
-  </si>
-  <si>
-    <t>sachsenring</t>
-  </si>
-  <si>
-    <t>Silverstone</t>
-  </si>
-  <si>
-    <t>silverstone 2019 gp</t>
-  </si>
-  <si>
-    <t>Skip Barber</t>
-  </si>
-  <si>
-    <t>barber 2026</t>
-  </si>
-  <si>
-    <t>Suzuka</t>
-  </si>
-  <si>
-    <t>suzuka grandprix</t>
-  </si>
-  <si>
-    <t>Zandvoort</t>
-  </si>
-  <si>
-    <t>zandvoort 2023 gp</t>
-  </si>
-  <si>
-    <t>Shell V-Power</t>
-  </si>
-  <si>
-    <t>thebend gt</t>
-  </si>
-  <si>
-    <t>Number of Corners</t>
-  </si>
-  <si>
-    <t>Average speed (mph)</t>
-  </si>
-  <si>
-    <t>Typical Lap Time, (seconds)</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
       <family val="2"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="10"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
+      <color rgb="FF000000"/>
+      <sz val="10"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color rgb="FF000000"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -206,39 +112,97 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+  <cellXfs count="9">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -538,236 +502,348 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E737F3EF-F3F9-42E9-80A3-35481F53397A}">
-  <dimension ref="A1:F11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.28515625" customWidth="1"/>
-    <col min="4" max="4" width="18.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="26.85546875" bestFit="1" customWidth="1"/>
+    <col width="13.5703125" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="19.7109375" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="13.28515625" customWidth="1" min="3" max="3"/>
+    <col width="18.28515625" bestFit="1" customWidth="1" min="4" max="4"/>
+    <col width="20.5703125" bestFit="1" customWidth="1" min="5" max="5"/>
+    <col width="26.85546875" bestFit="1" customWidth="1" min="6" max="6"/>
+    <col width="90" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" s="7">
+    <row r="1" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Track Name</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Track ID</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Length (ft)</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Number of Corners</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Average speed (mph)</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Typical Lap Time, (seconds)</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Track Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>Indianapolis</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>indianapolis 2022 road</t>
+        </is>
+      </c>
+      <c r="C2" s="7" t="n">
         <v>12878</v>
       </c>
-      <c r="D2" s="9">
+      <c r="D2" s="6" t="n">
         <v>14</v>
       </c>
-      <c r="E2" s="6">
+      <c r="E2" s="6" t="n">
         <v>102.7</v>
       </c>
-      <c r="F2">
+      <c r="F2" t="n">
         <v>85.5</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" s="7">
+      <c r="G2" s="8" t="inlineStr">
+        <is>
+          <t>Medium-low downforce. The long front straight and banked oval section give very high top speeds, followed by hard braking into Turn 1. The infield is tight and slow, with stop-and-go chicanes and 90-degree corners. Traction and clean exits matter more than mid-corner speed. Braking stability is key, and Turn 1 is the main overtaking spot.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Mobility Resort</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>twinring fullrc</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="n">
         <v>15752</v>
       </c>
-      <c r="D3" s="9">
+      <c r="D3" s="6" t="n">
         <v>14</v>
       </c>
-      <c r="E3" s="6">
+      <c r="E3" s="6" t="n">
         <v>98.5</v>
       </c>
-      <c r="F3">
+      <c r="F3" t="n">
         <v>109</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" s="7">
+      <c r="G3" s="8" t="inlineStr">
+        <is>
+          <t>Low-medium downforce. A stop-and-go layout with two long straights (one runs under the bridge) and several slow hairpins and 90-degree corners. It's all about heavy, stable braking and strong traction out of slow corners. Overtaking chances come under braking at the end of each straight. Hard on brakes; rear tires overheat from the repeated traction zones.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Monza</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>monza full</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="n">
         <v>19006</v>
       </c>
-      <c r="D4" s="9">
+      <c r="D4" s="6" t="n">
         <v>11</v>
       </c>
-      <c r="E4" s="6">
+      <c r="E4" s="6" t="n">
         <v>122.3</v>
       </c>
-      <c r="F4">
+      <c r="F4" t="n">
         <v>106</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" s="7">
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>Lowest downforce of the calendar. The highest top speeds, with long straights and slipstream battles. Very heavy braking into the tight chicanes (Rettifilo, Roggia, Ascari) calls for kerb-hopping and good car stability. The Lesmos and Parabolica are medium-to-fast corners where exit speed carries onto the straights. Trim wing and lean on the tow.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Road Atlanta</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>roadatlanta full</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="n">
         <v>13411</v>
       </c>
-      <c r="D5" s="9">
+      <c r="D5" s="6" t="n">
         <v>12</v>
       </c>
-      <c r="E5" s="6">
+      <c r="E5" s="6" t="n">
         <v>118</v>
       </c>
-      <c r="F5">
+      <c r="F5" t="n">
         <v>77.5</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6" s="7">
+      <c r="G5" s="8" t="inlineStr">
+        <is>
+          <t>Medium downforce with big elevation changes. The fast, blind, uphill Esses need commitment and a well-balanced car. A long back straight gives high top speed into heavy braking at the Turn 10 chicane. The fast downhill Turn 12 under the bridge leads onto the front straight. Bumpy; the car needs to ride the kerbs well.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Sachsenring</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>sachsenring</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="n">
         <v>12046</v>
       </c>
-      <c r="D6" s="9">
+      <c r="D6" s="6" t="n">
         <v>13</v>
       </c>
-      <c r="E6" s="6">
+      <c r="E6" s="6" t="n">
         <v>105.3</v>
       </c>
-      <c r="F6">
+      <c r="F6" t="n">
         <v>78</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B7" s="5" t="s">
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>High downforce, with a tight and twisty layout of short straights and mostly left-hand corners. The slow, technical infield rewards mechanical grip and rotation. The fast, blind, downhill 'Waterfall' (T11) needs confidence and stability. Low top speeds and limited overtaking make qualifying crucial. The left front tire takes a heavy load.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Silverstone</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>silverstone 2019 gp</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="n">
+        <v>19325</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>110.3</v>
+      </c>
+      <c r="F7" t="n">
+        <v>119.5</v>
+      </c>
+      <c r="G7" s="8" t="inlineStr">
+        <is>
+          <t>Medium-high downforce. A fast, flowing circuit whose Maggotts-Becketts-Chapel high-speed esses reward aero grip and quick changes of direction. The Hangar and Wellington straights provide good top speed and overtaking under braking into Stowe and Brooklands. Copse and Stowe are fast sweepers. The slower Loop/Luffield complex tests traction. Tire wear is high.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Skip Barber</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>barber 2026</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="n">
+        <v>12566</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>103.9</v>
+      </c>
+      <c r="F8" t="n">
+        <v>82.5</v>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>Medium-high downforce. A technical, flowing, rollercoaster-like track with lots of elevation change and few long straights. It mixes medium-speed sweepers with the tight Charlotte's Web hairpin. Top speeds stay moderate. Rhythm and precise lines matter more than power. Overtaking is difficult, and the constant loading is hard on tires.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Suzuka</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>suzuka grandprix</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="n">
+        <v>19050</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>107.8</v>
+      </c>
+      <c r="F9" t="n">
+        <v>120.5</v>
+      </c>
+      <c r="G9" s="8" t="inlineStr">
+        <is>
+          <t>Medium-high downforce on a figure-eight layout. The S-Curves demand rhythm and aero grip. Degner and the hairpin are slower, and Spoon is a long, fast corner. The long back straight through 130R gives the top speed of the lap, then heavy braking into the Casio Triangle chicane. Narrow with little room for error; it rewards a balanced car.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Zandvoort</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>zandvoort 2023 gp</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="n">
+        <v>13973</v>
+      </c>
+      <c r="D10" s="6" t="n">
         <v>14</v>
       </c>
-      <c r="C7" s="7">
-        <v>19325</v>
-      </c>
-      <c r="D7" s="9">
-        <v>18</v>
-      </c>
-      <c r="E7" s="6">
-        <v>110.3</v>
-      </c>
-      <c r="F7">
-        <v>119.5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C8" s="7">
-        <v>12566</v>
-      </c>
-      <c r="D8" s="9">
-        <v>16</v>
-      </c>
-      <c r="E8" s="6">
-        <v>103.9</v>
-      </c>
-      <c r="F8">
-        <v>82.5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C9" s="7">
-        <v>19050</v>
-      </c>
-      <c r="D9" s="9">
-        <v>17</v>
-      </c>
-      <c r="E9" s="6">
-        <v>107.8</v>
-      </c>
-      <c r="F9">
-        <v>120.5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C10" s="7">
-        <v>13973</v>
-      </c>
-      <c r="D10" s="9">
-        <v>14</v>
-      </c>
-      <c r="E10" s="6">
+      <c r="E10" s="6" t="n">
         <v>102.4</v>
       </c>
-      <c r="F10">
+      <c r="F10" t="n">
         <v>93</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C11" s="7">
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>High downforce. A narrow, undulating, old-school circuit with banked corners at Hugenholtz (T3) and the final Arie Luyendyk turn. There are few straights, so top speeds are modest, and blowing sand reduces grip. Fast, flowing sections through the dunes need a stable car. Overtaking is very hard; Tarzan (T1) is the main braking zone to pass.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Shell V-Power</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>thebend gt</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="n">
         <v>25492</v>
       </c>
-      <c r="D11" s="9">
+      <c r="D11" s="6" t="n">
         <v>35</v>
       </c>
-      <c r="E11" s="6">
+      <c r="E11" s="6" t="n">
         <v>99.3</v>
       </c>
-      <c r="F11">
+      <c r="F11" t="n">
         <v>175</v>
+      </c>
+      <c r="G11" s="8" t="inlineStr">
+        <is>
+          <t>Medium downforce as a compromise. The longest lap (35 corners) mixes several long straights with high top speeds, tight hairpins, 90-degree corners and fast sweepers. Heavy braking zones reward stability and good traction on exit. Wide and fairly flat with lots of runoff. The long lap makes consistency and tire management important.</t>
+        </is>
       </c>
     </row>
   </sheetData>
